--- a/Outcrop.xlsx
+++ b/Outcrop.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,6 +433,294 @@
         <v>19</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>11.46345452115031</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16.99527023737836</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>-2.481082735933585</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1.319215091428353</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.268224858303677</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.294714319022988</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>-3.611255654793011</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.920138691794293</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.185273983930662</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.139357421393388</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>-5.377150840510866</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2.859081817366074</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.024973382503131</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9.04154131445115</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>-7.13421655030013</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3.793330227309997</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4.911545852282919</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13.54779628858248</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>-6.672622027214357</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5.775307877961623</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5.945819031532874</v>
+      </c>
+      <c r="D9" t="n">
+        <v>15.28398524376398</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>-6.309441398693723</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5.940284004334776</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.49495689929484</v>
+      </c>
+      <c r="D10" t="n">
+        <v>18.5142678841708</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>-8.873623308232217</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4.718189205998202</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-7.287911310975932</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.048759558049339</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>-12.86856829900661</v>
+      </c>
+      <c r="B12" t="n">
+        <v>9.589734417367954</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-4.345204594563091</v>
+      </c>
+      <c r="D12" t="n">
+        <v>19.7474837331256</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>-8.812839966405992</v>
+      </c>
+      <c r="B13" t="n">
+        <v>7.957824941031663</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-1.405749090201624</v>
+      </c>
+      <c r="D13" t="n">
+        <v>19.36374466508943</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>-11.75203246095232</v>
+      </c>
+      <c r="B14" t="n">
+        <v>6.248666500680206</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-7.343784708481316</v>
+      </c>
+      <c r="D14" t="n">
+        <v>14.90033985054926</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>-10.92473727714776</v>
+      </c>
+      <c r="B15" t="n">
+        <v>9.965075331308556</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-3.325305718980314</v>
+      </c>
+      <c r="D15" t="n">
+        <v>21.23169594233158</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>-10.26318972511794</v>
+      </c>
+      <c r="B16" t="n">
+        <v>13.58050878971661</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-6.367600374079874</v>
+      </c>
+      <c r="D16" t="n">
+        <v>22.75794217863744</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>-15.31914073610239</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8.145331614335204</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-7.819461223945463</v>
+      </c>
+      <c r="D17" t="n">
+        <v>19.69382533494369</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-14.34349376044938</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10.80859781581078</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>-0.4414737964294635</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.2347357813929453</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.2175594218391147</v>
+      </c>
+      <c r="D19" t="n">
+        <v>13.06278171024945</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>-11.83149774430962</v>
+      </c>
+      <c r="B20" t="n">
+        <v>6.290918941330935</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.514472410750628</v>
+      </c>
+      <c r="D20" t="n">
+        <v>15.15091894133094</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>-11.47831870716605</v>
+      </c>
+      <c r="B21" t="n">
+        <v>6.103130316216579</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-13.59334925116021</v>
+      </c>
+      <c r="D21" t="n">
+        <v>10.8535666959581</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>-13.87993615974233</v>
+      </c>
+      <c r="B22" t="n">
+        <v>7.380092966994202</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-13.87993615974233</v>
+      </c>
+      <c r="D22" t="n">
+        <v>13.1500929669942</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
